--- a/results.xlsx
+++ b/results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACFDA70-6E13-43E5-9C66-B9E390F87D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5671946-4586-4312-B424-1B75EE7EEB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="97">
   <si>
     <t>yosef</t>
   </si>
@@ -319,6 +319,15 @@
   <si>
     <t>yosef-muhamad-michael4</t>
   </si>
+  <si>
+    <t>christian-yosef-muhamad</t>
+  </si>
+  <si>
+    <t>vasile-yosef-muhamad</t>
+  </si>
+  <si>
+    <t>vasile-yosef-muhamad2</t>
+  </si>
 </sst>
 </file>
 
@@ -525,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -544,6 +553,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -824,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX125"/>
+  <dimension ref="A1:AX134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -10389,11 +10400,11 @@
         <v>95.7</v>
       </c>
       <c r="G85" s="4">
-        <f t="shared" ref="G85:G108" si="40">ABS(C85-D85)</f>
+        <f t="shared" ref="G85:G117" si="40">ABS(C85-D85)</f>
         <v>0.40000000000000036</v>
       </c>
       <c r="H85" s="5">
-        <f t="shared" ref="H85:H108" si="41">ABS(E85-F85)</f>
+        <f t="shared" ref="H85:H117" si="41">ABS(E85-F85)</f>
         <v>2.7000000000000028</v>
       </c>
       <c r="L85" s="3" t="s">
@@ -10412,11 +10423,11 @@
         <v>106</v>
       </c>
       <c r="Q85" s="4">
-        <f t="shared" ref="Q85:Q108" si="42">ABS(M85-N85)</f>
+        <f t="shared" ref="Q85:Q117" si="42">ABS(M85-N85)</f>
         <v>0.80000000000000071</v>
       </c>
       <c r="R85" s="5">
-        <f t="shared" ref="R85:R108" si="43">ABS(O85-P85)</f>
+        <f t="shared" ref="R85:R117" si="43">ABS(O85-P85)</f>
         <v>13</v>
       </c>
       <c r="V85" s="3" t="s">
@@ -10435,11 +10446,11 @@
         <v>106.6</v>
       </c>
       <c r="AA85" s="4">
-        <f t="shared" ref="AA85:AA108" si="44">ABS(W85-X85)</f>
+        <f t="shared" ref="AA85:AA117" si="44">ABS(W85-X85)</f>
         <v>0.80000000000000071</v>
       </c>
       <c r="AB85" s="5">
-        <f t="shared" ref="AB85:AB108" si="45">ABS(Y85-Z85)</f>
+        <f t="shared" ref="AB85:AB117" si="45">ABS(Y85-Z85)</f>
         <v>13.599999999999994</v>
       </c>
       <c r="AG85" s="3" t="s">
@@ -10456,11 +10467,11 @@
         <v>133</v>
       </c>
       <c r="AL85" s="4">
-        <f t="shared" ref="AL85:AL108" si="46">ABS(AH85-AI85)</f>
+        <f t="shared" ref="AL85:AL117" si="46">ABS(AH85-AI85)</f>
         <v>16</v>
       </c>
       <c r="AM85" s="5">
-        <f t="shared" ref="AM85:AM108" si="47">ABS(AJ85-AK85)</f>
+        <f t="shared" ref="AM85:AM117" si="47">ABS(AJ85-AK85)</f>
         <v>40</v>
       </c>
       <c r="AR85" s="3" t="s">
@@ -10479,11 +10490,11 @@
         <v>107.3</v>
       </c>
       <c r="AW85" s="4">
-        <f t="shared" ref="AW85:AW108" si="48">ABS(AS85-AT85)</f>
+        <f t="shared" ref="AW85:AW117" si="48">ABS(AS85-AT85)</f>
         <v>0.80000000000000071</v>
       </c>
       <c r="AX85" s="5">
-        <f t="shared" ref="AX85:AX108" si="49">ABS(AU85-AV85)</f>
+        <f t="shared" ref="AX85:AX117" si="49">ABS(AU85-AV85)</f>
         <v>14.299999999999997</v>
       </c>
     </row>
@@ -12933,11 +12944,11 @@
       <c r="AK108" s="7">
         <v>112.5</v>
       </c>
-      <c r="AL108" s="7">
+      <c r="AL108" s="19">
         <f t="shared" si="46"/>
         <v>9.1999999999999993</v>
       </c>
-      <c r="AM108" s="8">
+      <c r="AM108" s="13">
         <f t="shared" si="47"/>
         <v>3.5</v>
       </c>
@@ -12965,1077 +12976,1089 @@
     </row>
     <row r="109" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B109" s="3" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="C109" s="4">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="D109" s="4">
-        <v>11.4</v>
+        <v>13</v>
       </c>
       <c r="E109" s="4">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F109" s="4">
-        <v>66.3</v>
-      </c>
-      <c r="G109">
-        <f t="shared" ref="G109:G124" si="50">ABS(C109-D109)</f>
+        <v>55</v>
+      </c>
+      <c r="G109" s="4">
+        <f t="shared" si="40"/>
         <v>0.19999999999999929</v>
       </c>
-      <c r="H109" s="13">
-        <f t="shared" ref="H109:H116" si="51">ABS(E109-F109)</f>
-        <v>25.700000000000003</v>
+      <c r="H109" s="5">
+        <f t="shared" si="41"/>
+        <v>48</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="M109" s="4">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="N109" s="4">
-        <v>10.7</v>
+        <v>13.4</v>
       </c>
       <c r="O109" s="4">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="P109" s="4">
-        <v>49.2</v>
+        <v>62.8</v>
       </c>
       <c r="Q109" s="4">
-        <f t="shared" ref="Q109:Q124" si="52">ABS(M109-N109)</f>
-        <v>0.90000000000000036</v>
+        <f t="shared" si="42"/>
+        <v>0.20000000000000107</v>
       </c>
       <c r="R109" s="5">
-        <f t="shared" ref="R109:R116" si="53">ABS(O109-P109)</f>
-        <v>42.8</v>
+        <f t="shared" si="43"/>
+        <v>40.200000000000003</v>
       </c>
       <c r="V109" s="3" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="W109" s="4">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="X109" s="4">
-        <v>11.7</v>
+        <v>12.9</v>
       </c>
       <c r="Y109" s="4">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="Z109" s="4">
-        <v>83.2</v>
+        <v>97</v>
       </c>
       <c r="AA109" s="4">
-        <f t="shared" ref="AA109:AA124" si="54">ABS(W109-X109)</f>
-        <v>9.9999999999999645E-2</v>
+        <f t="shared" si="44"/>
+        <v>0.29999999999999893</v>
       </c>
       <c r="AB109" s="5">
-        <f t="shared" ref="AB109:AB116" si="55">ABS(Y109-Z109)</f>
-        <v>8.7999999999999972</v>
+        <f t="shared" si="45"/>
+        <v>6</v>
       </c>
       <c r="AG109" s="3" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="AH109" s="4">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="AI109" s="4"/>
       <c r="AJ109" s="4">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="AK109" s="4">
-        <v>234</v>
+        <v>126</v>
       </c>
       <c r="AL109" s="4">
-        <f t="shared" ref="AL109:AL124" si="56">ABS(AH109-AI109)</f>
-        <v>11.6</v>
+        <f t="shared" si="46"/>
+        <v>13.2</v>
       </c>
       <c r="AM109" s="5">
-        <f t="shared" ref="AM109:AM116" si="57">ABS(AJ109-AK109)</f>
-        <v>142</v>
+        <f t="shared" si="47"/>
+        <v>23</v>
       </c>
       <c r="AR109" s="3" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="AS109" s="4">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="AT109" s="4">
-        <v>11.4</v>
+        <v>13</v>
       </c>
       <c r="AU109" s="4">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="AV109" s="4">
-        <v>62.9</v>
+        <v>39.6</v>
       </c>
       <c r="AW109" s="4">
-        <f t="shared" ref="AW109:AW124" si="58">ABS(AS109-AT109)</f>
+        <f t="shared" si="48"/>
         <v>0.19999999999999929</v>
       </c>
       <c r="AX109" s="5">
-        <f t="shared" ref="AX109:AX116" si="59">ABS(AU109-AV109)</f>
-        <v>29.1</v>
+        <f t="shared" si="49"/>
+        <v>63.4</v>
       </c>
     </row>
     <row r="110" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B110" s="12"/>
       <c r="C110">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D110">
-        <v>8.1999999999999993</v>
+        <v>7.3</v>
       </c>
       <c r="E110">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F110">
-        <v>69.400000000000006</v>
+        <v>82.6</v>
       </c>
       <c r="G110">
-        <f t="shared" si="50"/>
-        <v>1.8000000000000007</v>
+        <f t="shared" si="40"/>
+        <v>0.70000000000000018</v>
       </c>
       <c r="H110" s="13">
-        <f t="shared" si="51"/>
-        <v>1.5999999999999943</v>
+        <f t="shared" si="41"/>
+        <v>2.4000000000000057</v>
       </c>
       <c r="L110" s="12"/>
       <c r="M110">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N110">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="O110">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="P110">
-        <v>54</v>
+        <v>89.6</v>
       </c>
       <c r="Q110">
-        <f t="shared" si="52"/>
-        <v>0.59999999999999964</v>
+        <f t="shared" si="42"/>
+        <v>0.29999999999999982</v>
       </c>
       <c r="R110" s="13">
-        <f t="shared" si="53"/>
-        <v>17</v>
+        <f t="shared" si="43"/>
+        <v>4.5999999999999943</v>
       </c>
       <c r="V110" s="12"/>
       <c r="W110">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X110">
-        <v>8.1999999999999993</v>
+        <v>7</v>
       </c>
       <c r="Y110">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="Z110">
-        <v>96.7</v>
+        <v>94</v>
       </c>
       <c r="AA110">
-        <f t="shared" si="54"/>
-        <v>1.8000000000000007</v>
+        <f t="shared" si="44"/>
+        <v>1</v>
       </c>
       <c r="AB110" s="13">
-        <f t="shared" si="55"/>
-        <v>25.700000000000003</v>
+        <f t="shared" si="45"/>
+        <v>9</v>
       </c>
       <c r="AG110" s="12"/>
       <c r="AH110">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ110">
-        <v>71</v>
-      </c>
-      <c r="AK110">
-        <v>139</v>
-      </c>
-      <c r="AL110">
-        <f t="shared" si="56"/>
-        <v>10</v>
+        <v>85</v>
+      </c>
+      <c r="AK110" s="18">
+        <v>75.7</v>
+      </c>
+      <c r="AL110" s="19">
+        <f t="shared" si="46"/>
+        <v>8</v>
       </c>
       <c r="AM110" s="13">
-        <f t="shared" si="57"/>
-        <v>68</v>
+        <f t="shared" si="47"/>
+        <v>9.2999999999999972</v>
       </c>
       <c r="AR110" s="12"/>
       <c r="AS110">
-        <v>10</v>
-      </c>
-      <c r="AT110">
         <v>8</v>
       </c>
+      <c r="AT110" s="18">
+        <v>7.4</v>
+      </c>
       <c r="AU110">
-        <v>71</v>
-      </c>
-      <c r="AV110">
-        <v>63.2</v>
-      </c>
-      <c r="AW110">
-        <f t="shared" si="58"/>
-        <v>2</v>
+        <v>85</v>
+      </c>
+      <c r="AV110" s="18">
+        <v>89.9</v>
+      </c>
+      <c r="AW110" s="18">
+        <f t="shared" si="48"/>
+        <v>0.59999999999999964</v>
       </c>
       <c r="AX110" s="13">
-        <f t="shared" si="59"/>
-        <v>7.7999999999999972</v>
+        <f t="shared" si="49"/>
+        <v>4.9000000000000057</v>
       </c>
     </row>
     <row r="111" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B111" s="12"/>
-      <c r="C111">
-        <v>11.2</v>
-      </c>
-      <c r="D111">
-        <v>11</v>
-      </c>
-      <c r="E111">
-        <v>105</v>
-      </c>
-      <c r="F111">
-        <v>62</v>
+      <c r="B111" s="6"/>
+      <c r="C111" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="D111" s="7">
+        <v>7</v>
+      </c>
+      <c r="E111" s="7">
+        <v>71</v>
+      </c>
+      <c r="F111" s="7">
+        <v>68.099999999999994</v>
       </c>
       <c r="G111">
-        <f t="shared" si="50"/>
-        <v>0.19999999999999929</v>
+        <f t="shared" si="40"/>
+        <v>0.20000000000000018</v>
       </c>
       <c r="H111" s="13">
-        <f t="shared" si="51"/>
-        <v>43</v>
-      </c>
-      <c r="L111" s="12"/>
-      <c r="M111">
-        <v>11.2</v>
-      </c>
-      <c r="N111">
-        <v>10.4</v>
-      </c>
-      <c r="O111">
-        <v>105</v>
-      </c>
-      <c r="P111">
-        <v>62.8</v>
-      </c>
-      <c r="Q111">
-        <f t="shared" si="52"/>
-        <v>0.79999999999999893</v>
-      </c>
-      <c r="R111" s="13">
-        <f t="shared" si="53"/>
-        <v>42.2</v>
-      </c>
-      <c r="V111" s="12"/>
-      <c r="W111">
-        <v>11.2</v>
-      </c>
-      <c r="X111">
-        <v>10.5</v>
-      </c>
-      <c r="Y111">
-        <v>105</v>
-      </c>
-      <c r="Z111">
-        <v>85</v>
+        <f t="shared" si="41"/>
+        <v>2.9000000000000057</v>
+      </c>
+      <c r="L111" s="6"/>
+      <c r="M111" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="N111" s="7">
+        <v>7.3</v>
+      </c>
+      <c r="O111" s="7">
+        <v>71</v>
+      </c>
+      <c r="P111" s="7">
+        <v>50.4</v>
+      </c>
+      <c r="Q111" s="7">
+        <f t="shared" si="42"/>
+        <v>9.9999999999999645E-2</v>
+      </c>
+      <c r="R111" s="8">
+        <f t="shared" si="43"/>
+        <v>20.6</v>
+      </c>
+      <c r="V111" s="6"/>
+      <c r="W111" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="X111" s="7">
+        <v>7</v>
+      </c>
+      <c r="Y111" s="7">
+        <v>71</v>
+      </c>
+      <c r="Z111" s="7">
+        <v>101.4</v>
       </c>
       <c r="AA111">
-        <f t="shared" si="54"/>
-        <v>0.69999999999999929</v>
+        <f t="shared" si="44"/>
+        <v>0.20000000000000018</v>
       </c>
       <c r="AB111" s="13">
-        <f t="shared" si="55"/>
-        <v>20</v>
-      </c>
-      <c r="AG111" s="12"/>
-      <c r="AH111">
-        <v>11.2</v>
-      </c>
-      <c r="AJ111">
-        <v>105</v>
-      </c>
-      <c r="AK111">
-        <v>69.5</v>
-      </c>
-      <c r="AL111">
-        <f t="shared" si="56"/>
-        <v>11.2</v>
-      </c>
-      <c r="AM111" s="13">
-        <f t="shared" si="57"/>
-        <v>35.5</v>
-      </c>
-      <c r="AR111" s="12"/>
-      <c r="AS111">
-        <v>11.2</v>
-      </c>
-      <c r="AT111">
-        <v>11.4</v>
-      </c>
-      <c r="AU111">
-        <v>105</v>
-      </c>
-      <c r="AV111">
-        <v>59.3</v>
-      </c>
-      <c r="AW111">
-        <f t="shared" si="58"/>
-        <v>0.20000000000000107</v>
+        <f t="shared" si="45"/>
+        <v>30.400000000000006</v>
+      </c>
+      <c r="AG111" s="6"/>
+      <c r="AH111" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="AI111" s="7"/>
+      <c r="AJ111" s="7">
+        <v>71</v>
+      </c>
+      <c r="AK111" s="7">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="AL111" s="7">
+        <f t="shared" si="46"/>
+        <v>7.2</v>
+      </c>
+      <c r="AM111" s="8">
+        <f t="shared" si="47"/>
+        <v>1.4000000000000057</v>
+      </c>
+      <c r="AR111" s="6"/>
+      <c r="AS111" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="AT111" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="AU111" s="7">
+        <v>71</v>
+      </c>
+      <c r="AV111" s="7">
+        <v>92.4</v>
+      </c>
+      <c r="AW111" s="19">
+        <f t="shared" si="48"/>
+        <v>0</v>
       </c>
       <c r="AX111" s="13">
-        <f t="shared" si="59"/>
-        <v>45.7</v>
+        <f t="shared" si="49"/>
+        <v>21.400000000000006</v>
       </c>
     </row>
     <row r="112" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B112" s="6"/>
-      <c r="C112" s="7">
-        <v>10.4</v>
-      </c>
-      <c r="D112" s="7">
-        <v>10.7</v>
-      </c>
-      <c r="E112" s="7">
-        <v>72</v>
-      </c>
-      <c r="F112" s="7">
-        <v>68.8</v>
-      </c>
-      <c r="G112" s="7">
-        <f t="shared" si="50"/>
-        <v>0.29999999999999893</v>
-      </c>
-      <c r="H112" s="8">
-        <f t="shared" si="51"/>
-        <v>3.2000000000000028</v>
-      </c>
-      <c r="L112" s="6"/>
-      <c r="M112" s="7">
-        <v>10.4</v>
-      </c>
-      <c r="N112" s="7">
-        <v>10.1</v>
-      </c>
-      <c r="O112" s="7">
-        <v>72</v>
-      </c>
-      <c r="P112" s="7">
-        <v>69.599999999999994</v>
-      </c>
-      <c r="Q112" s="7">
-        <f t="shared" si="52"/>
-        <v>0.30000000000000071</v>
-      </c>
-      <c r="R112" s="8">
-        <f t="shared" si="53"/>
-        <v>2.4000000000000057</v>
-      </c>
-      <c r="V112" s="6"/>
-      <c r="W112" s="7">
-        <v>10.4</v>
-      </c>
-      <c r="X112" s="7">
+      <c r="B112" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C112" s="4">
+        <v>10</v>
+      </c>
+      <c r="D112" s="4">
+        <v>10</v>
+      </c>
+      <c r="E112" s="4">
+        <v>78</v>
+      </c>
+      <c r="F112" s="4">
+        <v>60</v>
+      </c>
+      <c r="G112" s="4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="H112" s="5">
+        <f t="shared" si="41"/>
+        <v>18</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M112" s="4">
+        <v>10</v>
+      </c>
+      <c r="N112" s="4">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="O112" s="4">
+        <v>78</v>
+      </c>
+      <c r="P112" s="4">
+        <v>59.2</v>
+      </c>
+      <c r="Q112" s="4">
+        <f t="shared" si="42"/>
+        <v>0.19999999999999929</v>
+      </c>
+      <c r="R112" s="5">
+        <f t="shared" si="43"/>
+        <v>18.799999999999997</v>
+      </c>
+      <c r="V112" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="W112" s="4">
+        <v>10</v>
+      </c>
+      <c r="X112" s="4">
         <v>10.5</v>
       </c>
-      <c r="Y112" s="7">
-        <v>72</v>
-      </c>
-      <c r="Z112" s="7">
-        <v>84</v>
-      </c>
-      <c r="AA112" s="7">
-        <f t="shared" si="54"/>
-        <v>9.9999999999999645E-2</v>
-      </c>
-      <c r="AB112" s="8">
-        <f t="shared" si="55"/>
+      <c r="Y112" s="4">
+        <v>78</v>
+      </c>
+      <c r="Z112" s="4">
+        <v>79.7</v>
+      </c>
+      <c r="AA112" s="4">
+        <f t="shared" si="44"/>
+        <v>0.5</v>
+      </c>
+      <c r="AB112" s="5">
+        <f t="shared" si="45"/>
+        <v>1.7000000000000028</v>
+      </c>
+      <c r="AG112" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH112" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI112" s="4"/>
+      <c r="AJ112" s="4">
+        <v>78</v>
+      </c>
+      <c r="AK112" s="4">
+        <v>66</v>
+      </c>
+      <c r="AL112" s="4">
+        <f t="shared" si="46"/>
+        <v>10</v>
+      </c>
+      <c r="AM112" s="5">
+        <f t="shared" si="47"/>
         <v>12</v>
       </c>
-      <c r="AG112" s="6"/>
-      <c r="AH112" s="7">
-        <v>10.4</v>
-      </c>
-      <c r="AI112" s="7"/>
-      <c r="AJ112" s="7">
-        <v>72</v>
-      </c>
-      <c r="AK112" s="7">
-        <v>82.3</v>
-      </c>
-      <c r="AL112" s="7">
-        <f t="shared" si="56"/>
-        <v>10.4</v>
-      </c>
-      <c r="AM112" s="8">
-        <f t="shared" si="57"/>
-        <v>10.299999999999997</v>
-      </c>
-      <c r="AR112" s="6"/>
-      <c r="AS112" s="7">
-        <v>10.4</v>
-      </c>
-      <c r="AT112" s="7">
-        <v>10.6</v>
-      </c>
-      <c r="AU112" s="7">
-        <v>72</v>
-      </c>
-      <c r="AV112" s="7">
-        <v>67</v>
-      </c>
-      <c r="AW112" s="7">
-        <f t="shared" si="58"/>
-        <v>0.19999999999999929</v>
-      </c>
-      <c r="AX112" s="8">
-        <f t="shared" si="59"/>
-        <v>5</v>
+      <c r="AR112" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS112" s="4">
+        <v>10</v>
+      </c>
+      <c r="AT112" s="4">
+        <v>10</v>
+      </c>
+      <c r="AU112" s="4">
+        <v>78</v>
+      </c>
+      <c r="AV112" s="4">
+        <v>54.8</v>
+      </c>
+      <c r="AW112" s="4">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="AX112" s="5">
+        <f t="shared" si="49"/>
+        <v>23.200000000000003</v>
       </c>
     </row>
     <row r="113" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B113" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C113" s="4">
-        <v>12.8</v>
-      </c>
-      <c r="D113" s="4">
-        <v>12.3</v>
-      </c>
-      <c r="E113" s="4">
-        <v>95</v>
-      </c>
-      <c r="F113" s="4">
-        <v>56.6</v>
+      <c r="B113" s="12"/>
+      <c r="C113">
+        <v>8</v>
+      </c>
+      <c r="D113">
+        <v>7.7</v>
+      </c>
+      <c r="E113">
+        <v>74</v>
+      </c>
+      <c r="F113">
+        <v>78.8</v>
       </c>
       <c r="G113">
-        <f t="shared" si="50"/>
-        <v>0.5</v>
+        <f t="shared" si="40"/>
+        <v>0.29999999999999982</v>
       </c>
       <c r="H113" s="13">
-        <f t="shared" si="51"/>
-        <v>38.4</v>
-      </c>
-      <c r="L113" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M113" s="4">
-        <v>12.8</v>
-      </c>
-      <c r="N113" s="4">
-        <v>12.9</v>
-      </c>
-      <c r="O113" s="4">
-        <v>95</v>
-      </c>
-      <c r="P113" s="4">
-        <v>50</v>
+        <f t="shared" si="41"/>
+        <v>4.7999999999999972</v>
+      </c>
+      <c r="L113" s="12"/>
+      <c r="M113">
+        <v>8</v>
+      </c>
+      <c r="N113">
+        <v>7.7</v>
+      </c>
+      <c r="O113">
+        <v>74</v>
+      </c>
+      <c r="P113">
+        <v>64</v>
       </c>
       <c r="Q113">
-        <f t="shared" si="52"/>
-        <v>9.9999999999999645E-2</v>
+        <f t="shared" si="42"/>
+        <v>0.29999999999999982</v>
       </c>
       <c r="R113" s="13">
-        <f t="shared" si="53"/>
-        <v>45</v>
-      </c>
-      <c r="V113" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="W113" s="4">
-        <v>12.8</v>
-      </c>
-      <c r="X113" s="4">
-        <v>12.9</v>
-      </c>
-      <c r="Y113" s="4">
-        <v>95</v>
-      </c>
-      <c r="Z113" s="4">
-        <v>95.5</v>
+        <f t="shared" si="43"/>
+        <v>10</v>
+      </c>
+      <c r="V113" s="12"/>
+      <c r="W113">
+        <v>8</v>
+      </c>
+      <c r="X113">
+        <v>7</v>
+      </c>
+      <c r="Y113">
+        <v>74</v>
+      </c>
+      <c r="Z113">
+        <v>92.9</v>
       </c>
       <c r="AA113">
-        <f t="shared" si="54"/>
-        <v>9.9999999999999645E-2</v>
+        <f t="shared" si="44"/>
+        <v>1</v>
       </c>
       <c r="AB113" s="13">
-        <f t="shared" si="55"/>
-        <v>0.5</v>
-      </c>
-      <c r="AG113" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH113" s="4">
-        <v>12.8</v>
-      </c>
-      <c r="AI113" s="4"/>
-      <c r="AJ113" s="4">
-        <v>95</v>
-      </c>
-      <c r="AK113" s="4">
-        <v>150</v>
-      </c>
-      <c r="AL113">
-        <f t="shared" si="56"/>
-        <v>12.8</v>
+        <f t="shared" si="45"/>
+        <v>18.900000000000006</v>
+      </c>
+      <c r="AG113" s="12"/>
+      <c r="AH113">
+        <v>8</v>
+      </c>
+      <c r="AJ113">
+        <v>74</v>
+      </c>
+      <c r="AK113" s="18">
+        <v>110.5</v>
+      </c>
+      <c r="AL113" s="19">
+        <f t="shared" si="46"/>
+        <v>8</v>
       </c>
       <c r="AM113" s="13">
-        <f t="shared" si="57"/>
-        <v>55</v>
-      </c>
-      <c r="AR113" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AS113" s="4">
-        <v>12.8</v>
-      </c>
-      <c r="AT113" s="4">
-        <v>12.4</v>
-      </c>
-      <c r="AU113" s="4">
-        <v>95</v>
-      </c>
-      <c r="AV113" s="4">
-        <v>57.6</v>
-      </c>
-      <c r="AW113">
-        <f t="shared" si="58"/>
-        <v>0.40000000000000036</v>
+        <f t="shared" si="47"/>
+        <v>36.5</v>
+      </c>
+      <c r="AR113" s="12"/>
+      <c r="AS113">
+        <v>8</v>
+      </c>
+      <c r="AT113" s="18">
+        <v>6.8</v>
+      </c>
+      <c r="AU113">
+        <v>74</v>
+      </c>
+      <c r="AV113" s="18">
+        <v>87.7</v>
+      </c>
+      <c r="AW113" s="19">
+        <f t="shared" si="48"/>
+        <v>1.2000000000000002</v>
       </c>
       <c r="AX113" s="13">
-        <f t="shared" si="59"/>
-        <v>37.4</v>
+        <f t="shared" si="49"/>
+        <v>13.700000000000003</v>
       </c>
     </row>
     <row r="114" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B114" s="12"/>
-      <c r="C114">
-        <v>10</v>
-      </c>
-      <c r="D114">
-        <v>10</v>
-      </c>
-      <c r="E114">
-        <v>76</v>
-      </c>
-      <c r="F114">
-        <v>63.9</v>
+      <c r="B114" s="6"/>
+      <c r="C114" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="D114" s="7">
+        <v>7.3</v>
+      </c>
+      <c r="E114" s="7">
+        <v>70</v>
+      </c>
+      <c r="F114" s="7">
+        <v>72.5</v>
       </c>
       <c r="G114">
-        <f t="shared" si="50"/>
-        <v>0</v>
+        <f t="shared" si="40"/>
+        <v>9.9999999999999645E-2</v>
       </c>
       <c r="H114" s="13">
-        <f t="shared" si="51"/>
-        <v>12.100000000000001</v>
-      </c>
-      <c r="L114" s="12"/>
-      <c r="M114">
-        <v>10</v>
-      </c>
-      <c r="N114">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="O114">
-        <v>76</v>
-      </c>
-      <c r="P114">
-        <v>58.4</v>
-      </c>
-      <c r="Q114">
-        <f t="shared" si="52"/>
-        <v>0.19999999999999929</v>
-      </c>
-      <c r="R114" s="13">
-        <f t="shared" si="53"/>
-        <v>17.600000000000001</v>
-      </c>
-      <c r="V114" s="12"/>
-      <c r="W114">
-        <v>10</v>
-      </c>
-      <c r="X114">
-        <v>10.5</v>
-      </c>
-      <c r="Y114">
-        <v>76</v>
-      </c>
-      <c r="Z114">
-        <v>80.599999999999994</v>
+        <f t="shared" si="41"/>
+        <v>2.5</v>
+      </c>
+      <c r="L114" s="6"/>
+      <c r="M114" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="N114" s="7">
+        <v>6.6</v>
+      </c>
+      <c r="O114" s="7">
+        <v>70</v>
+      </c>
+      <c r="P114" s="7">
+        <v>51.2</v>
+      </c>
+      <c r="Q114" s="7">
+        <f t="shared" si="42"/>
+        <v>0.60000000000000053</v>
+      </c>
+      <c r="R114" s="8">
+        <f t="shared" si="43"/>
+        <v>18.799999999999997</v>
+      </c>
+      <c r="V114" s="6"/>
+      <c r="W114" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="X114" s="7">
+        <v>7</v>
+      </c>
+      <c r="Y114" s="7">
+        <v>70</v>
+      </c>
+      <c r="Z114" s="7">
+        <v>96.1</v>
       </c>
       <c r="AA114">
-        <f t="shared" si="54"/>
-        <v>0.5</v>
+        <f t="shared" si="44"/>
+        <v>0.20000000000000018</v>
       </c>
       <c r="AB114" s="13">
-        <f t="shared" si="55"/>
-        <v>4.5999999999999943</v>
-      </c>
-      <c r="AG114" s="12"/>
-      <c r="AH114">
-        <v>10</v>
-      </c>
-      <c r="AJ114">
-        <v>76</v>
-      </c>
-      <c r="AK114">
-        <v>61</v>
-      </c>
-      <c r="AL114">
-        <f t="shared" si="56"/>
-        <v>10</v>
-      </c>
-      <c r="AM114" s="13">
-        <f t="shared" si="57"/>
-        <v>15</v>
-      </c>
-      <c r="AR114" s="12"/>
-      <c r="AS114">
-        <v>10</v>
-      </c>
-      <c r="AT114">
-        <v>10</v>
-      </c>
-      <c r="AU114">
-        <v>76</v>
-      </c>
-      <c r="AV114">
-        <v>69.599999999999994</v>
-      </c>
-      <c r="AW114">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="AX114" s="13">
-        <f t="shared" si="59"/>
-        <v>6.4000000000000057</v>
+        <f t="shared" si="45"/>
+        <v>26.099999999999994</v>
+      </c>
+      <c r="AG114" s="6"/>
+      <c r="AH114" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="AI114" s="7"/>
+      <c r="AJ114" s="7">
+        <v>70</v>
+      </c>
+      <c r="AK114" s="7">
+        <v>105.6</v>
+      </c>
+      <c r="AL114" s="7">
+        <f t="shared" si="46"/>
+        <v>7.2</v>
+      </c>
+      <c r="AM114" s="8">
+        <f t="shared" si="47"/>
+        <v>35.599999999999994</v>
+      </c>
+      <c r="AR114" s="6"/>
+      <c r="AS114" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="AT114" s="7">
+        <v>6.4</v>
+      </c>
+      <c r="AU114" s="7">
+        <v>70</v>
+      </c>
+      <c r="AV114" s="7">
+        <v>54</v>
+      </c>
+      <c r="AW114" s="7">
+        <f t="shared" si="48"/>
+        <v>0.79999999999999982</v>
+      </c>
+      <c r="AX114" s="8">
+        <f t="shared" si="49"/>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B115" s="12"/>
-      <c r="C115">
-        <v>10</v>
-      </c>
-      <c r="D115">
-        <v>9</v>
-      </c>
-      <c r="E115">
-        <v>72</v>
-      </c>
-      <c r="F115">
-        <v>66</v>
-      </c>
-      <c r="G115">
-        <f t="shared" si="50"/>
-        <v>1</v>
-      </c>
-      <c r="H115" s="13">
-        <f t="shared" si="51"/>
-        <v>6</v>
-      </c>
-      <c r="L115" s="12"/>
-      <c r="M115">
-        <v>10</v>
-      </c>
-      <c r="N115">
-        <v>9.5</v>
-      </c>
-      <c r="O115">
-        <v>72</v>
-      </c>
-      <c r="P115">
-        <v>50.8</v>
-      </c>
-      <c r="Q115">
-        <f t="shared" si="52"/>
-        <v>0.5</v>
-      </c>
-      <c r="R115" s="13">
-        <f t="shared" si="53"/>
-        <v>21.200000000000003</v>
-      </c>
-      <c r="V115" s="12"/>
-      <c r="W115">
-        <v>10</v>
-      </c>
-      <c r="X115">
-        <v>9.4</v>
-      </c>
-      <c r="Y115">
-        <v>72</v>
-      </c>
-      <c r="Z115">
-        <v>79.7</v>
-      </c>
-      <c r="AA115">
-        <f t="shared" si="54"/>
-        <v>0.59999999999999964</v>
-      </c>
-      <c r="AB115" s="13">
-        <f t="shared" si="55"/>
-        <v>7.7000000000000028</v>
-      </c>
-      <c r="AG115" s="12"/>
-      <c r="AH115">
-        <v>10</v>
-      </c>
-      <c r="AJ115">
-        <v>72</v>
-      </c>
-      <c r="AK115">
-        <v>72.7</v>
-      </c>
-      <c r="AL115">
-        <f t="shared" si="56"/>
-        <v>10</v>
-      </c>
-      <c r="AM115" s="13">
-        <f t="shared" si="57"/>
-        <v>0.70000000000000284</v>
-      </c>
-      <c r="AR115" s="12"/>
-      <c r="AS115">
-        <v>10</v>
-      </c>
-      <c r="AT115">
-        <v>9.6</v>
-      </c>
-      <c r="AU115">
-        <v>72</v>
-      </c>
-      <c r="AV115">
-        <v>57.3</v>
-      </c>
-      <c r="AW115">
-        <f t="shared" si="58"/>
-        <v>0.40000000000000036</v>
-      </c>
-      <c r="AX115" s="13">
-        <f t="shared" si="59"/>
-        <v>14.700000000000003</v>
+      <c r="B115" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C115" s="4">
+        <v>8</v>
+      </c>
+      <c r="D115" s="4">
+        <v>8.1</v>
+      </c>
+      <c r="E115" s="4">
+        <v>70</v>
+      </c>
+      <c r="F115" s="4">
+        <v>66.3</v>
+      </c>
+      <c r="G115" s="4">
+        <f t="shared" si="40"/>
+        <v>9.9999999999999645E-2</v>
+      </c>
+      <c r="H115" s="5">
+        <f t="shared" si="41"/>
+        <v>3.7000000000000028</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M115" s="4">
+        <v>8</v>
+      </c>
+      <c r="N115" s="4">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="O115" s="4">
+        <v>70</v>
+      </c>
+      <c r="P115" s="4">
+        <v>62.8</v>
+      </c>
+      <c r="Q115" s="4">
+        <f t="shared" si="42"/>
+        <v>1.1999999999999993</v>
+      </c>
+      <c r="R115" s="5">
+        <f t="shared" si="43"/>
+        <v>7.2000000000000028</v>
+      </c>
+      <c r="V115" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="W115" s="4">
+        <v>8</v>
+      </c>
+      <c r="X115" s="4">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Y115" s="4">
+        <v>70</v>
+      </c>
+      <c r="Z115" s="4">
+        <v>90.8</v>
+      </c>
+      <c r="AA115" s="4">
+        <f t="shared" si="44"/>
+        <v>0.19999999999999929</v>
+      </c>
+      <c r="AB115" s="5">
+        <f t="shared" si="45"/>
+        <v>20.799999999999997</v>
+      </c>
+      <c r="AG115" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH115" s="4">
+        <v>8</v>
+      </c>
+      <c r="AI115" s="4"/>
+      <c r="AJ115" s="4">
+        <v>70</v>
+      </c>
+      <c r="AK115" s="4">
+        <v>101</v>
+      </c>
+      <c r="AL115" s="4">
+        <f t="shared" si="46"/>
+        <v>8</v>
+      </c>
+      <c r="AM115" s="5">
+        <f t="shared" si="47"/>
+        <v>31</v>
+      </c>
+      <c r="AR115" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS115" s="4">
+        <v>8</v>
+      </c>
+      <c r="AT115" s="4">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AU115" s="4">
+        <v>70</v>
+      </c>
+      <c r="AV115" s="4">
+        <v>61.8</v>
+      </c>
+      <c r="AW115" s="4">
+        <f t="shared" si="48"/>
+        <v>0.19999999999999929</v>
+      </c>
+      <c r="AX115" s="5">
+        <f t="shared" si="49"/>
+        <v>8.2000000000000028</v>
       </c>
     </row>
     <row r="116" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B116" s="6"/>
-      <c r="C116" s="7">
-        <v>10</v>
-      </c>
-      <c r="D116" s="7">
-        <v>10.8</v>
-      </c>
-      <c r="E116" s="7">
-        <v>102</v>
-      </c>
-      <c r="F116" s="7">
-        <v>81</v>
-      </c>
-      <c r="G116" s="7">
-        <f t="shared" si="50"/>
-        <v>0.80000000000000071</v>
+      <c r="B116" s="12"/>
+      <c r="C116">
+        <v>10.4</v>
+      </c>
+      <c r="D116">
+        <v>10.4</v>
+      </c>
+      <c r="E116">
+        <v>85</v>
+      </c>
+      <c r="F116">
+        <v>73.400000000000006</v>
+      </c>
+      <c r="G116">
+        <f t="shared" si="40"/>
+        <v>0</v>
       </c>
       <c r="H116" s="13">
-        <f t="shared" si="51"/>
-        <v>21</v>
-      </c>
-      <c r="L116" s="6"/>
-      <c r="M116" s="7">
-        <v>10</v>
-      </c>
-      <c r="N116" s="7">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="O116" s="7">
-        <v>102</v>
-      </c>
-      <c r="P116" s="7">
-        <v>102</v>
-      </c>
-      <c r="Q116" s="7">
-        <f t="shared" si="52"/>
-        <v>0.30000000000000071</v>
-      </c>
-      <c r="R116" s="8">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="V116" s="6"/>
-      <c r="W116" s="7">
-        <v>10</v>
-      </c>
-      <c r="X116" s="7">
-        <v>10</v>
-      </c>
-      <c r="Y116" s="7">
-        <v>102</v>
-      </c>
-      <c r="Z116" s="7">
-        <v>101</v>
-      </c>
-      <c r="AA116" s="7">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AB116" s="8">
-        <f t="shared" si="55"/>
-        <v>1</v>
-      </c>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="7">
-        <v>10</v>
-      </c>
-      <c r="AI116" s="7"/>
-      <c r="AJ116" s="7">
-        <v>102</v>
-      </c>
-      <c r="AK116" s="7">
-        <v>136.80000000000001</v>
-      </c>
-      <c r="AL116" s="7">
-        <f t="shared" si="56"/>
-        <v>10</v>
-      </c>
-      <c r="AM116" s="8">
-        <f t="shared" si="57"/>
-        <v>34.800000000000011</v>
-      </c>
-      <c r="AR116" s="6"/>
-      <c r="AS116" s="7">
-        <v>10</v>
-      </c>
-      <c r="AT116" s="7">
-        <v>10.5</v>
-      </c>
-      <c r="AU116" s="7">
-        <v>102</v>
-      </c>
-      <c r="AV116" s="7">
-        <v>84</v>
-      </c>
-      <c r="AW116" s="7">
-        <f t="shared" si="58"/>
-        <v>0.5</v>
-      </c>
-      <c r="AX116" s="8">
-        <f t="shared" si="59"/>
-        <v>18</v>
+        <f t="shared" si="41"/>
+        <v>11.599999999999994</v>
+      </c>
+      <c r="L116" s="12"/>
+      <c r="M116">
+        <v>10.4</v>
+      </c>
+      <c r="N116">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="O116">
+        <v>85</v>
+      </c>
+      <c r="P116">
+        <v>114.8</v>
+      </c>
+      <c r="Q116">
+        <f t="shared" si="42"/>
+        <v>0.20000000000000107</v>
+      </c>
+      <c r="R116" s="13">
+        <f t="shared" si="43"/>
+        <v>29.799999999999997</v>
+      </c>
+      <c r="V116" s="12"/>
+      <c r="W116">
+        <v>10.4</v>
+      </c>
+      <c r="X116">
+        <v>7</v>
+      </c>
+      <c r="Y116">
+        <v>85</v>
+      </c>
+      <c r="Z116">
+        <v>92.3</v>
+      </c>
+      <c r="AA116">
+        <f t="shared" si="44"/>
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="AB116" s="13">
+        <f t="shared" si="45"/>
+        <v>7.2999999999999972</v>
+      </c>
+      <c r="AG116" s="12"/>
+      <c r="AH116">
+        <v>10.4</v>
+      </c>
+      <c r="AJ116">
+        <v>85</v>
+      </c>
+      <c r="AK116" s="18">
+        <v>97.3</v>
+      </c>
+      <c r="AL116" s="19">
+        <f t="shared" si="46"/>
+        <v>10.4</v>
+      </c>
+      <c r="AM116" s="13">
+        <f t="shared" si="47"/>
+        <v>12.299999999999997</v>
+      </c>
+      <c r="AR116" s="12"/>
+      <c r="AS116">
+        <v>10.4</v>
+      </c>
+      <c r="AT116" s="18">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AU116">
+        <v>85</v>
+      </c>
+      <c r="AV116" s="18">
+        <v>114.8</v>
+      </c>
+      <c r="AW116" s="19">
+        <f t="shared" si="48"/>
+        <v>2.2000000000000011</v>
+      </c>
+      <c r="AX116" s="13">
+        <f t="shared" si="49"/>
+        <v>29.799999999999997</v>
       </c>
     </row>
     <row r="117" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C117" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="D117" s="4">
-        <v>10</v>
-      </c>
-      <c r="E117" s="4">
-        <v>91</v>
-      </c>
-      <c r="F117" s="4">
-        <v>68.8</v>
-      </c>
-      <c r="G117" s="4">
-        <f t="shared" si="50"/>
-        <v>0.80000000000000071</v>
-      </c>
-      <c r="H117" s="5">
-        <f>ABS(F117-E117)</f>
-        <v>22.200000000000003</v>
-      </c>
-      <c r="L117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M117" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="N117" s="4">
-        <v>10</v>
-      </c>
-      <c r="O117" s="4">
-        <v>91</v>
-      </c>
-      <c r="P117" s="4">
-        <v>118.8</v>
-      </c>
-      <c r="Q117" s="4">
-        <f t="shared" si="52"/>
-        <v>0.80000000000000071</v>
-      </c>
-      <c r="R117" s="5">
-        <f>ABS(P117-O117)</f>
-        <v>27.799999999999997</v>
-      </c>
-      <c r="V117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="W117" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="X117" s="4">
-        <v>10</v>
-      </c>
-      <c r="Y117" s="4">
-        <v>91</v>
-      </c>
-      <c r="Z117" s="4">
-        <v>81.2</v>
-      </c>
-      <c r="AA117" s="4">
-        <f t="shared" si="54"/>
-        <v>0.80000000000000071</v>
-      </c>
-      <c r="AB117" s="5">
-        <f>ABS(Z117-Y117)</f>
-        <v>9.7999999999999972</v>
-      </c>
-      <c r="AG117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH117" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="AI117" s="4"/>
-      <c r="AJ117" s="4">
-        <v>91</v>
-      </c>
-      <c r="AK117" s="4">
-        <v>114.6</v>
-      </c>
-      <c r="AL117" s="4">
-        <f t="shared" si="56"/>
-        <v>10.8</v>
-      </c>
-      <c r="AM117" s="5">
-        <f>ABS(AK117-AJ117)</f>
-        <v>23.599999999999994</v>
-      </c>
-      <c r="AR117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AS117" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="AT117" s="4">
-        <v>10</v>
-      </c>
-      <c r="AU117" s="4">
-        <v>91</v>
-      </c>
-      <c r="AV117" s="4">
-        <v>64.400000000000006</v>
-      </c>
-      <c r="AW117" s="4">
-        <f t="shared" si="58"/>
-        <v>0.80000000000000071</v>
-      </c>
-      <c r="AX117" s="5">
-        <f>ABS(AV117-AU117)</f>
-        <v>26.599999999999994</v>
+      <c r="B117" s="6"/>
+      <c r="C117" s="7">
+        <v>8</v>
+      </c>
+      <c r="D117" s="7">
+        <v>8.4</v>
+      </c>
+      <c r="E117" s="7">
+        <v>68</v>
+      </c>
+      <c r="F117" s="7">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="G117" s="7">
+        <f t="shared" si="40"/>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="H117" s="8">
+        <f t="shared" si="41"/>
+        <v>8.0999999999999943</v>
+      </c>
+      <c r="L117" s="6"/>
+      <c r="M117" s="7">
+        <v>8</v>
+      </c>
+      <c r="N117" s="7">
+        <v>9.4</v>
+      </c>
+      <c r="O117" s="7">
+        <v>68</v>
+      </c>
+      <c r="P117" s="7">
+        <v>59.6</v>
+      </c>
+      <c r="Q117" s="7">
+        <f t="shared" si="42"/>
+        <v>1.4000000000000004</v>
+      </c>
+      <c r="R117" s="8">
+        <f t="shared" si="43"/>
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="V117" s="6"/>
+      <c r="W117" s="7">
+        <v>8</v>
+      </c>
+      <c r="X117" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="Y117" s="7">
+        <v>68</v>
+      </c>
+      <c r="Z117" s="7">
+        <v>94.3</v>
+      </c>
+      <c r="AA117" s="7">
+        <f t="shared" si="44"/>
+        <v>0.5</v>
+      </c>
+      <c r="AB117" s="8">
+        <f t="shared" si="45"/>
+        <v>26.299999999999997</v>
+      </c>
+      <c r="AG117" s="6"/>
+      <c r="AH117" s="7">
+        <v>8</v>
+      </c>
+      <c r="AI117" s="7"/>
+      <c r="AJ117" s="7">
+        <v>68</v>
+      </c>
+      <c r="AK117" s="7">
+        <v>83.75</v>
+      </c>
+      <c r="AL117" s="7">
+        <f t="shared" si="46"/>
+        <v>8</v>
+      </c>
+      <c r="AM117" s="8">
+        <f t="shared" si="47"/>
+        <v>15.75</v>
+      </c>
+      <c r="AR117" s="6"/>
+      <c r="AS117" s="7">
+        <v>8</v>
+      </c>
+      <c r="AT117" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="AU117" s="7">
+        <v>68</v>
+      </c>
+      <c r="AV117" s="7">
+        <v>53</v>
+      </c>
+      <c r="AW117" s="7">
+        <f t="shared" si="48"/>
+        <v>1.5</v>
+      </c>
+      <c r="AX117" s="8">
+        <f t="shared" si="49"/>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B118" s="12"/>
-      <c r="C118">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="D118">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="E118">
-        <v>94</v>
-      </c>
-      <c r="F118">
-        <v>69.3</v>
+      <c r="B118" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" s="4">
+        <v>11.6</v>
+      </c>
+      <c r="D118" s="4">
+        <v>11.4</v>
+      </c>
+      <c r="E118" s="4">
+        <v>92</v>
+      </c>
+      <c r="F118" s="4">
+        <v>66.3</v>
       </c>
       <c r="G118">
-        <f t="shared" si="50"/>
-        <v>0.60000000000000142</v>
+        <f t="shared" ref="G118:G133" si="50">ABS(C118-D118)</f>
+        <v>0.19999999999999929</v>
       </c>
       <c r="H118" s="13">
-        <f t="shared" ref="H118:H124" si="60">ABS(F118-E118)</f>
-        <v>24.700000000000003</v>
-      </c>
-      <c r="L118" s="12"/>
-      <c r="M118">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="N118">
-        <v>9.4</v>
-      </c>
-      <c r="O118">
-        <v>94</v>
-      </c>
-      <c r="P118">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="Q118">
-        <f t="shared" si="52"/>
-        <v>0.59999999999999964</v>
-      </c>
-      <c r="R118" s="13">
-        <f t="shared" ref="R118:R124" si="61">ABS(P118-O118)</f>
-        <v>17.599999999999994</v>
-      </c>
-      <c r="V118" s="12"/>
-      <c r="W118">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="X118">
-        <v>7.3</v>
-      </c>
-      <c r="Y118">
-        <v>94</v>
-      </c>
-      <c r="Z118">
-        <v>83.5</v>
+        <f t="shared" ref="H118:H125" si="51">ABS(E118-F118)</f>
+        <v>25.700000000000003</v>
+      </c>
+      <c r="L118" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M118" s="4">
+        <v>11.6</v>
+      </c>
+      <c r="N118" s="4">
+        <v>10.7</v>
+      </c>
+      <c r="O118" s="4">
+        <v>92</v>
+      </c>
+      <c r="P118" s="4">
+        <v>49.2</v>
+      </c>
+      <c r="Q118" s="4">
+        <f t="shared" ref="Q118:Q133" si="52">ABS(M118-N118)</f>
+        <v>0.90000000000000036</v>
+      </c>
+      <c r="R118" s="5">
+        <f t="shared" ref="R118:R125" si="53">ABS(O118-P118)</f>
+        <v>42.8</v>
+      </c>
+      <c r="V118" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W118" s="4">
+        <v>11.6</v>
+      </c>
+      <c r="X118" s="4">
+        <v>11.7</v>
+      </c>
+      <c r="Y118" s="4">
+        <v>92</v>
+      </c>
+      <c r="Z118" s="4">
+        <v>83.2</v>
       </c>
       <c r="AA118">
-        <f t="shared" si="54"/>
-        <v>1.5000000000000009</v>
+        <f t="shared" ref="AA118:AA133" si="54">ABS(W118-X118)</f>
+        <v>9.9999999999999645E-2</v>
       </c>
       <c r="AB118" s="13">
-        <f t="shared" ref="AB118:AB124" si="62">ABS(Z118-Y118)</f>
-        <v>10.5</v>
-      </c>
-      <c r="AG118" s="12"/>
-      <c r="AH118">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AJ118">
-        <v>94</v>
-      </c>
-      <c r="AK118">
-        <v>74.5</v>
-      </c>
-      <c r="AL118">
-        <f t="shared" si="56"/>
-        <v>8.8000000000000007</v>
+        <f t="shared" ref="AB118:AB125" si="55">ABS(Y118-Z118)</f>
+        <v>8.7999999999999972</v>
+      </c>
+      <c r="AG118" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH118" s="4">
+        <v>11.6</v>
+      </c>
+      <c r="AI118" s="4"/>
+      <c r="AJ118" s="4">
+        <v>92</v>
+      </c>
+      <c r="AK118" s="4">
+        <v>234</v>
+      </c>
+      <c r="AL118" s="19">
+        <f t="shared" ref="AL118:AL133" si="56">ABS(AH118-AI118)</f>
+        <v>11.6</v>
       </c>
       <c r="AM118" s="13">
-        <f t="shared" ref="AM118:AM124" si="63">ABS(AK118-AJ118)</f>
-        <v>19.5</v>
-      </c>
-      <c r="AR118" s="12"/>
-      <c r="AS118">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AT118">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AU118">
-        <v>94</v>
-      </c>
-      <c r="AV118">
-        <v>78.900000000000006</v>
-      </c>
-      <c r="AW118">
-        <f t="shared" si="58"/>
-        <v>0</v>
+        <f t="shared" ref="AM118:AM125" si="57">ABS(AJ118-AK118)</f>
+        <v>142</v>
+      </c>
+      <c r="AR118" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS118" s="4">
+        <v>11.6</v>
+      </c>
+      <c r="AT118" s="4">
+        <v>11.4</v>
+      </c>
+      <c r="AU118" s="4">
+        <v>92</v>
+      </c>
+      <c r="AV118" s="4">
+        <v>62.9</v>
+      </c>
+      <c r="AW118" s="19">
+        <f t="shared" ref="AW118:AW133" si="58">ABS(AS118-AT118)</f>
+        <v>0.19999999999999929</v>
       </c>
       <c r="AX118" s="13">
-        <f t="shared" ref="AX118:AX124" si="64">ABS(AV118-AU118)</f>
-        <v>15.099999999999994</v>
+        <f t="shared" ref="AX118:AX125" si="59">ABS(AU118-AV118)</f>
+        <v>29.1</v>
       </c>
     </row>
     <row r="119" spans="2:50" x14ac:dyDescent="0.25">
@@ -14044,426 +14067,426 @@
         <v>10</v>
       </c>
       <c r="D119">
-        <v>9.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E119">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F119">
-        <v>78.400000000000006</v>
+        <v>69.400000000000006</v>
       </c>
       <c r="G119">
         <f t="shared" si="50"/>
-        <v>0.5</v>
+        <v>1.8000000000000007</v>
       </c>
       <c r="H119" s="13">
-        <f t="shared" si="60"/>
-        <v>2.4000000000000057</v>
+        <f t="shared" si="51"/>
+        <v>1.5999999999999943</v>
       </c>
       <c r="L119" s="12"/>
       <c r="M119">
         <v>10</v>
       </c>
       <c r="N119">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="O119">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P119">
-        <v>85.6</v>
+        <v>54</v>
       </c>
       <c r="Q119">
         <f t="shared" si="52"/>
-        <v>0.40000000000000036</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="R119" s="13">
-        <f t="shared" si="61"/>
-        <v>9.5999999999999943</v>
+        <f t="shared" si="53"/>
+        <v>17</v>
       </c>
       <c r="V119" s="12"/>
       <c r="W119">
         <v>10</v>
       </c>
       <c r="X119">
-        <v>9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="Y119">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="Z119">
-        <v>77.599999999999994</v>
+        <v>96.7</v>
       </c>
       <c r="AA119">
         <f t="shared" si="54"/>
-        <v>1</v>
+        <v>1.8000000000000007</v>
       </c>
       <c r="AB119" s="13">
-        <f t="shared" si="62"/>
-        <v>1.5999999999999943</v>
+        <f t="shared" si="55"/>
+        <v>25.700000000000003</v>
       </c>
       <c r="AG119" s="12"/>
       <c r="AH119">
         <v>10</v>
       </c>
       <c r="AJ119">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="AK119">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="AL119">
         <f t="shared" si="56"/>
         <v>10</v>
       </c>
       <c r="AM119" s="13">
-        <f t="shared" si="63"/>
-        <v>96</v>
+        <f t="shared" si="57"/>
+        <v>68</v>
       </c>
       <c r="AR119" s="12"/>
       <c r="AS119">
         <v>10</v>
       </c>
       <c r="AT119">
-        <v>10.15</v>
+        <v>8</v>
       </c>
       <c r="AU119">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="AV119">
-        <v>89.7</v>
+        <v>63.2</v>
       </c>
       <c r="AW119">
         <f t="shared" si="58"/>
-        <v>0.15000000000000036</v>
+        <v>2</v>
       </c>
       <c r="AX119" s="13">
-        <f t="shared" si="64"/>
-        <v>13.700000000000003</v>
+        <f t="shared" si="59"/>
+        <v>7.7999999999999972</v>
       </c>
     </row>
     <row r="120" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B120" s="6"/>
-      <c r="C120" s="7">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="D120" s="7">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="E120" s="7">
-        <v>94</v>
-      </c>
-      <c r="F120" s="7">
-        <v>83.2</v>
-      </c>
-      <c r="G120" s="7">
+      <c r="B120" s="12"/>
+      <c r="C120">
+        <v>11.2</v>
+      </c>
+      <c r="D120">
+        <v>11</v>
+      </c>
+      <c r="E120">
+        <v>105</v>
+      </c>
+      <c r="F120">
+        <v>62</v>
+      </c>
+      <c r="G120">
         <f t="shared" si="50"/>
-        <v>0.89999999999999858</v>
+        <v>0.19999999999999929</v>
       </c>
       <c r="H120" s="13">
-        <f t="shared" si="60"/>
-        <v>10.799999999999997</v>
-      </c>
-      <c r="L120" s="6"/>
-      <c r="M120" s="7">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="N120" s="7">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="O120" s="7">
-        <v>94</v>
-      </c>
-      <c r="P120" s="7">
-        <v>113</v>
-      </c>
-      <c r="Q120" s="7">
+        <f t="shared" si="51"/>
+        <v>43</v>
+      </c>
+      <c r="L120" s="12"/>
+      <c r="M120">
+        <v>11.2</v>
+      </c>
+      <c r="N120">
+        <v>10.4</v>
+      </c>
+      <c r="O120">
+        <v>105</v>
+      </c>
+      <c r="P120">
+        <v>62.8</v>
+      </c>
+      <c r="Q120">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0.79999999999999893</v>
       </c>
       <c r="R120" s="13">
-        <f t="shared" si="61"/>
-        <v>19</v>
-      </c>
-      <c r="V120" s="6"/>
-      <c r="W120" s="7">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="X120" s="7">
-        <v>9</v>
-      </c>
-      <c r="Y120" s="7">
-        <v>94</v>
-      </c>
-      <c r="Z120" s="7">
-        <v>87</v>
-      </c>
-      <c r="AA120" s="7">
+        <f t="shared" si="53"/>
+        <v>42.2</v>
+      </c>
+      <c r="V120" s="12"/>
+      <c r="W120">
+        <v>11.2</v>
+      </c>
+      <c r="X120">
+        <v>10.5</v>
+      </c>
+      <c r="Y120">
+        <v>105</v>
+      </c>
+      <c r="Z120">
+        <v>85</v>
+      </c>
+      <c r="AA120">
         <f t="shared" si="54"/>
-        <v>0.19999999999999929</v>
+        <v>0.69999999999999929</v>
       </c>
       <c r="AB120" s="13">
-        <f t="shared" si="62"/>
-        <v>7</v>
-      </c>
-      <c r="AG120" s="6"/>
-      <c r="AH120" s="7">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AI120" s="7"/>
-      <c r="AJ120" s="7">
-        <v>94</v>
-      </c>
-      <c r="AK120" s="7">
-        <v>165</v>
-      </c>
-      <c r="AL120" s="7">
+        <f t="shared" si="55"/>
+        <v>20</v>
+      </c>
+      <c r="AG120" s="12"/>
+      <c r="AH120">
+        <v>11.2</v>
+      </c>
+      <c r="AJ120">
+        <v>105</v>
+      </c>
+      <c r="AK120">
+        <v>69.5</v>
+      </c>
+      <c r="AL120">
         <f t="shared" si="56"/>
-        <v>8.8000000000000007</v>
+        <v>11.2</v>
       </c>
       <c r="AM120" s="13">
-        <f t="shared" si="63"/>
-        <v>71</v>
-      </c>
-      <c r="AR120" s="6"/>
-      <c r="AS120" s="7">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AT120" s="7">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="AU120" s="7">
-        <v>94</v>
-      </c>
-      <c r="AV120" s="7">
-        <v>68.900000000000006</v>
-      </c>
-      <c r="AW120" s="7">
+        <f t="shared" si="57"/>
+        <v>35.5</v>
+      </c>
+      <c r="AR120" s="12"/>
+      <c r="AS120">
+        <v>11.2</v>
+      </c>
+      <c r="AT120">
+        <v>11.4</v>
+      </c>
+      <c r="AU120">
+        <v>105</v>
+      </c>
+      <c r="AV120">
+        <v>59.3</v>
+      </c>
+      <c r="AW120">
         <f t="shared" si="58"/>
-        <v>0.39999999999999858</v>
+        <v>0.20000000000000107</v>
       </c>
       <c r="AX120" s="13">
-        <f t="shared" si="64"/>
-        <v>25.099999999999994</v>
+        <f t="shared" si="59"/>
+        <v>45.7</v>
       </c>
     </row>
     <row r="121" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B121" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C121" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="D121" s="4">
+      <c r="B121" s="6"/>
+      <c r="C121" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="D121" s="7">
         <v>10.7</v>
       </c>
-      <c r="E121" s="4">
-        <v>95</v>
-      </c>
-      <c r="F121" s="4">
-        <v>68.7</v>
-      </c>
-      <c r="G121" s="4">
+      <c r="E121" s="7">
+        <v>72</v>
+      </c>
+      <c r="F121" s="7">
+        <v>68.8</v>
+      </c>
+      <c r="G121" s="7">
         <f t="shared" si="50"/>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="H121" s="5">
-        <f t="shared" si="60"/>
-        <v>26.299999999999997</v>
-      </c>
-      <c r="L121" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M121" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="N121" s="4">
+        <v>0.29999999999999893</v>
+      </c>
+      <c r="H121" s="8">
+        <f t="shared" si="51"/>
+        <v>3.2000000000000028</v>
+      </c>
+      <c r="L121" s="6"/>
+      <c r="M121" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="N121" s="7">
         <v>10.1</v>
       </c>
-      <c r="O121" s="4">
-        <v>95</v>
-      </c>
-      <c r="P121" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="Q121" s="4">
+      <c r="O121" s="7">
+        <v>72</v>
+      </c>
+      <c r="P121" s="7">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="Q121" s="7">
         <f t="shared" si="52"/>
-        <v>0.70000000000000107</v>
-      </c>
-      <c r="R121" s="5">
-        <f t="shared" si="61"/>
-        <v>1.4000000000000057</v>
-      </c>
-      <c r="V121" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W121" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="X121" s="4">
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="R121" s="8">
+        <f t="shared" si="53"/>
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="V121" s="6"/>
+      <c r="W121" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="X121" s="7">
         <v>10.5</v>
       </c>
-      <c r="Y121" s="4">
-        <v>95</v>
-      </c>
-      <c r="Z121" s="4">
-        <v>88.5</v>
-      </c>
-      <c r="AA121" s="4">
+      <c r="Y121" s="7">
+        <v>72</v>
+      </c>
+      <c r="Z121" s="7">
+        <v>84</v>
+      </c>
+      <c r="AA121" s="7">
         <f t="shared" si="54"/>
-        <v>0.30000000000000071</v>
-      </c>
-      <c r="AB121" s="5">
-        <f t="shared" si="62"/>
-        <v>6.5</v>
-      </c>
-      <c r="AG121" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH121" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="AI121" s="4"/>
-      <c r="AJ121" s="4">
-        <v>95</v>
-      </c>
-      <c r="AK121" s="4">
-        <v>106.5</v>
-      </c>
-      <c r="AL121" s="4">
+        <v>9.9999999999999645E-2</v>
+      </c>
+      <c r="AB121" s="8">
+        <f t="shared" si="55"/>
+        <v>12</v>
+      </c>
+      <c r="AG121" s="6"/>
+      <c r="AH121" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="AI121" s="7"/>
+      <c r="AJ121" s="7">
+        <v>72</v>
+      </c>
+      <c r="AK121" s="7">
+        <v>82.3</v>
+      </c>
+      <c r="AL121" s="7">
         <f t="shared" si="56"/>
-        <v>10.8</v>
-      </c>
-      <c r="AM121" s="5">
-        <f t="shared" si="63"/>
-        <v>11.5</v>
-      </c>
-      <c r="AR121" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AS121" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="AT121" s="4">
+        <v>10.4</v>
+      </c>
+      <c r="AM121" s="8">
+        <f t="shared" si="57"/>
+        <v>10.299999999999997</v>
+      </c>
+      <c r="AR121" s="6"/>
+      <c r="AS121" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="AT121" s="7">
         <v>10.6</v>
       </c>
-      <c r="AU121" s="4">
-        <v>95</v>
-      </c>
-      <c r="AV121" s="4">
-        <v>86.7</v>
-      </c>
-      <c r="AW121" s="4">
+      <c r="AU121" s="7">
+        <v>72</v>
+      </c>
+      <c r="AV121" s="7">
+        <v>67</v>
+      </c>
+      <c r="AW121" s="7">
         <f t="shared" si="58"/>
-        <v>0.20000000000000107</v>
-      </c>
-      <c r="AX121" s="5">
-        <f t="shared" si="64"/>
-        <v>8.2999999999999972</v>
+        <v>0.19999999999999929</v>
+      </c>
+      <c r="AX121" s="8">
+        <f t="shared" si="59"/>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B122" s="12"/>
-      <c r="C122">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="D122">
-        <v>8.9</v>
-      </c>
-      <c r="E122">
-        <v>101</v>
-      </c>
-      <c r="F122">
-        <v>72.599999999999994</v>
+      <c r="B122" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C122" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="D122" s="4">
+        <v>12.3</v>
+      </c>
+      <c r="E122" s="4">
+        <v>95</v>
+      </c>
+      <c r="F122" s="4">
+        <v>56.6</v>
       </c>
       <c r="G122">
         <f t="shared" si="50"/>
-        <v>0.29999999999999893</v>
+        <v>0.5</v>
       </c>
       <c r="H122" s="13">
-        <f t="shared" si="60"/>
-        <v>28.400000000000006</v>
-      </c>
-      <c r="L122" s="12"/>
-      <c r="M122">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="N122">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="O122">
-        <v>101</v>
-      </c>
-      <c r="P122">
-        <v>50.5</v>
+        <f t="shared" si="51"/>
+        <v>38.4</v>
+      </c>
+      <c r="L122" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M122" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="N122" s="4">
+        <v>12.9</v>
+      </c>
+      <c r="O122" s="4">
+        <v>95</v>
+      </c>
+      <c r="P122" s="4">
+        <v>50</v>
       </c>
       <c r="Q122">
         <f t="shared" si="52"/>
-        <v>0.10000000000000142</v>
+        <v>9.9999999999999645E-2</v>
       </c>
       <c r="R122" s="13">
-        <f t="shared" si="61"/>
-        <v>50.5</v>
-      </c>
-      <c r="V122" s="12"/>
-      <c r="W122">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="X122">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="Y122">
-        <v>101</v>
-      </c>
-      <c r="Z122">
-        <v>95.8</v>
+        <f t="shared" si="53"/>
+        <v>45</v>
+      </c>
+      <c r="V122" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W122" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="X122" s="4">
+        <v>12.9</v>
+      </c>
+      <c r="Y122" s="4">
+        <v>95</v>
+      </c>
+      <c r="Z122" s="4">
+        <v>95.5</v>
       </c>
       <c r="AA122">
         <f t="shared" si="54"/>
-        <v>1</v>
+        <v>9.9999999999999645E-2</v>
       </c>
       <c r="AB122" s="13">
-        <f t="shared" si="62"/>
-        <v>5.2000000000000028</v>
-      </c>
-      <c r="AG122" s="12"/>
-      <c r="AH122">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="AJ122">
-        <v>101</v>
-      </c>
-      <c r="AK122">
-        <v>64.3</v>
+        <f t="shared" si="55"/>
+        <v>0.5</v>
+      </c>
+      <c r="AG122" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH122" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="AI122" s="4"/>
+      <c r="AJ122" s="4">
+        <v>95</v>
+      </c>
+      <c r="AK122" s="4">
+        <v>150</v>
       </c>
       <c r="AL122">
         <f t="shared" si="56"/>
-        <v>9.1999999999999993</v>
+        <v>12.8</v>
       </c>
       <c r="AM122" s="13">
-        <f t="shared" si="63"/>
-        <v>36.700000000000003</v>
-      </c>
-      <c r="AR122" s="12"/>
-      <c r="AS122">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="AT122">
-        <v>8.6</v>
-      </c>
-      <c r="AU122">
-        <v>101</v>
-      </c>
-      <c r="AV122">
-        <v>64.3</v>
+        <f t="shared" si="57"/>
+        <v>55</v>
+      </c>
+      <c r="AR122" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AS122" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="AT122" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="AU122" s="4">
+        <v>95</v>
+      </c>
+      <c r="AV122" s="4">
+        <v>57.6</v>
       </c>
       <c r="AW122">
         <f t="shared" si="58"/>
-        <v>0.59999999999999964</v>
+        <v>0.40000000000000036</v>
       </c>
       <c r="AX122" s="13">
-        <f t="shared" si="64"/>
-        <v>36.700000000000003</v>
+        <f t="shared" si="59"/>
+        <v>37.4</v>
       </c>
     </row>
     <row r="123" spans="2:50" x14ac:dyDescent="0.25">
@@ -14472,245 +14495,1205 @@
         <v>10</v>
       </c>
       <c r="D123">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="E123">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F123">
-        <v>70.8</v>
+        <v>63.9</v>
       </c>
       <c r="G123">
         <f t="shared" si="50"/>
-        <v>2.9000000000000004</v>
+        <v>0</v>
       </c>
       <c r="H123" s="13">
-        <f t="shared" si="60"/>
-        <v>19.200000000000003</v>
+        <f t="shared" si="51"/>
+        <v>12.100000000000001</v>
       </c>
       <c r="L123" s="12"/>
       <c r="M123">
         <v>10</v>
       </c>
       <c r="N123">
-        <v>8.8000000000000007</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="O123">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="P123">
-        <v>58.8</v>
+        <v>58.4</v>
       </c>
       <c r="Q123">
         <f t="shared" si="52"/>
-        <v>1.1999999999999993</v>
+        <v>0.19999999999999929</v>
       </c>
       <c r="R123" s="13">
-        <f t="shared" si="61"/>
-        <v>31.200000000000003</v>
+        <f t="shared" si="53"/>
+        <v>17.600000000000001</v>
       </c>
       <c r="V123" s="12"/>
       <c r="W123">
         <v>10</v>
       </c>
       <c r="X123">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="Y123">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="Z123">
-        <v>88.5</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="AA123">
         <f t="shared" si="54"/>
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AB123" s="13">
-        <f t="shared" si="62"/>
-        <v>1.5</v>
+        <f t="shared" si="55"/>
+        <v>4.5999999999999943</v>
       </c>
       <c r="AG123" s="12"/>
       <c r="AH123">
         <v>10</v>
       </c>
       <c r="AJ123">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="AK123">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="AL123">
         <f t="shared" si="56"/>
         <v>10</v>
       </c>
       <c r="AM123" s="13">
-        <f t="shared" si="63"/>
-        <v>12</v>
+        <f t="shared" si="57"/>
+        <v>15</v>
       </c>
       <c r="AR123" s="12"/>
       <c r="AS123">
         <v>10</v>
       </c>
       <c r="AT123">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AU123">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="AV123">
-        <v>75.599999999999994</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="AW123">
         <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AX123" s="13">
+        <f t="shared" si="59"/>
+        <v>6.4000000000000057</v>
+      </c>
+    </row>
+    <row r="124" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B124" s="12"/>
+      <c r="C124">
+        <v>10</v>
+      </c>
+      <c r="D124">
+        <v>9</v>
+      </c>
+      <c r="E124">
+        <v>72</v>
+      </c>
+      <c r="F124">
+        <v>66</v>
+      </c>
+      <c r="G124">
+        <f t="shared" si="50"/>
+        <v>1</v>
+      </c>
+      <c r="H124" s="13">
+        <f t="shared" si="51"/>
+        <v>6</v>
+      </c>
+      <c r="L124" s="12"/>
+      <c r="M124">
+        <v>10</v>
+      </c>
+      <c r="N124">
+        <v>9.5</v>
+      </c>
+      <c r="O124">
+        <v>72</v>
+      </c>
+      <c r="P124">
+        <v>50.8</v>
+      </c>
+      <c r="Q124">
+        <f t="shared" si="52"/>
+        <v>0.5</v>
+      </c>
+      <c r="R124" s="13">
+        <f t="shared" si="53"/>
+        <v>21.200000000000003</v>
+      </c>
+      <c r="V124" s="12"/>
+      <c r="W124">
+        <v>10</v>
+      </c>
+      <c r="X124">
+        <v>9.4</v>
+      </c>
+      <c r="Y124">
+        <v>72</v>
+      </c>
+      <c r="Z124">
+        <v>79.7</v>
+      </c>
+      <c r="AA124">
+        <f t="shared" si="54"/>
+        <v>0.59999999999999964</v>
+      </c>
+      <c r="AB124" s="13">
+        <f t="shared" si="55"/>
+        <v>7.7000000000000028</v>
+      </c>
+      <c r="AG124" s="12"/>
+      <c r="AH124">
+        <v>10</v>
+      </c>
+      <c r="AJ124">
+        <v>72</v>
+      </c>
+      <c r="AK124">
+        <v>72.7</v>
+      </c>
+      <c r="AL124">
+        <f t="shared" si="56"/>
+        <v>10</v>
+      </c>
+      <c r="AM124" s="13">
+        <f t="shared" si="57"/>
+        <v>0.70000000000000284</v>
+      </c>
+      <c r="AR124" s="12"/>
+      <c r="AS124">
+        <v>10</v>
+      </c>
+      <c r="AT124">
+        <v>9.6</v>
+      </c>
+      <c r="AU124">
+        <v>72</v>
+      </c>
+      <c r="AV124">
+        <v>57.3</v>
+      </c>
+      <c r="AW124">
+        <f t="shared" si="58"/>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="AX124" s="13">
+        <f t="shared" si="59"/>
+        <v>14.700000000000003</v>
+      </c>
+    </row>
+    <row r="125" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B125" s="6"/>
+      <c r="C125" s="7">
+        <v>10</v>
+      </c>
+      <c r="D125" s="7">
+        <v>10.8</v>
+      </c>
+      <c r="E125" s="7">
+        <v>102</v>
+      </c>
+      <c r="F125" s="7">
+        <v>81</v>
+      </c>
+      <c r="G125" s="7">
+        <f t="shared" si="50"/>
+        <v>0.80000000000000071</v>
+      </c>
+      <c r="H125" s="13">
+        <f t="shared" si="51"/>
+        <v>21</v>
+      </c>
+      <c r="L125" s="6"/>
+      <c r="M125" s="7">
+        <v>10</v>
+      </c>
+      <c r="N125" s="7">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="O125" s="7">
+        <v>102</v>
+      </c>
+      <c r="P125" s="7">
+        <v>102</v>
+      </c>
+      <c r="Q125" s="7">
+        <f t="shared" si="52"/>
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="R125" s="8">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="V125" s="6"/>
+      <c r="W125" s="7">
+        <v>10</v>
+      </c>
+      <c r="X125" s="7">
+        <v>10</v>
+      </c>
+      <c r="Y125" s="7">
+        <v>102</v>
+      </c>
+      <c r="Z125" s="7">
+        <v>101</v>
+      </c>
+      <c r="AA125" s="7">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="AB125" s="8">
+        <f t="shared" si="55"/>
+        <v>1</v>
+      </c>
+      <c r="AG125" s="6"/>
+      <c r="AH125" s="7">
+        <v>10</v>
+      </c>
+      <c r="AI125" s="7"/>
+      <c r="AJ125" s="7">
+        <v>102</v>
+      </c>
+      <c r="AK125" s="7">
+        <v>136.80000000000001</v>
+      </c>
+      <c r="AL125" s="7">
+        <f t="shared" si="56"/>
+        <v>10</v>
+      </c>
+      <c r="AM125" s="8">
+        <f t="shared" si="57"/>
+        <v>34.800000000000011</v>
+      </c>
+      <c r="AR125" s="6"/>
+      <c r="AS125" s="7">
+        <v>10</v>
+      </c>
+      <c r="AT125" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="AU125" s="7">
+        <v>102</v>
+      </c>
+      <c r="AV125" s="7">
+        <v>84</v>
+      </c>
+      <c r="AW125" s="7">
+        <f t="shared" si="58"/>
+        <v>0.5</v>
+      </c>
+      <c r="AX125" s="8">
+        <f t="shared" si="59"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B126" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C126" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="D126" s="4">
+        <v>10</v>
+      </c>
+      <c r="E126" s="4">
+        <v>91</v>
+      </c>
+      <c r="F126" s="4">
+        <v>68.8</v>
+      </c>
+      <c r="G126" s="4">
+        <f t="shared" si="50"/>
+        <v>0.80000000000000071</v>
+      </c>
+      <c r="H126" s="5">
+        <f>ABS(F126-E126)</f>
+        <v>22.200000000000003</v>
+      </c>
+      <c r="L126" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M126" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="N126" s="4">
+        <v>10</v>
+      </c>
+      <c r="O126" s="4">
+        <v>91</v>
+      </c>
+      <c r="P126" s="4">
+        <v>118.8</v>
+      </c>
+      <c r="Q126" s="4">
+        <f t="shared" si="52"/>
+        <v>0.80000000000000071</v>
+      </c>
+      <c r="R126" s="5">
+        <f>ABS(P126-O126)</f>
+        <v>27.799999999999997</v>
+      </c>
+      <c r="V126" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="W126" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="X126" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y126" s="4">
+        <v>91</v>
+      </c>
+      <c r="Z126" s="4">
+        <v>81.2</v>
+      </c>
+      <c r="AA126" s="4">
+        <f t="shared" si="54"/>
+        <v>0.80000000000000071</v>
+      </c>
+      <c r="AB126" s="5">
+        <f>ABS(Z126-Y126)</f>
+        <v>9.7999999999999972</v>
+      </c>
+      <c r="AG126" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH126" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="AI126" s="4"/>
+      <c r="AJ126" s="4">
+        <v>91</v>
+      </c>
+      <c r="AK126" s="4">
+        <v>114.6</v>
+      </c>
+      <c r="AL126" s="4">
+        <f t="shared" si="56"/>
+        <v>10.8</v>
+      </c>
+      <c r="AM126" s="5">
+        <f>ABS(AK126-AJ126)</f>
+        <v>23.599999999999994</v>
+      </c>
+      <c r="AR126" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AS126" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="AT126" s="4">
+        <v>10</v>
+      </c>
+      <c r="AU126" s="4">
+        <v>91</v>
+      </c>
+      <c r="AV126" s="4">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="AW126" s="4">
+        <f t="shared" si="58"/>
+        <v>0.80000000000000071</v>
+      </c>
+      <c r="AX126" s="5">
+        <f>ABS(AV126-AU126)</f>
+        <v>26.599999999999994</v>
+      </c>
+    </row>
+    <row r="127" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B127" s="12"/>
+      <c r="C127">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D127">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E127">
+        <v>94</v>
+      </c>
+      <c r="F127">
+        <v>69.3</v>
+      </c>
+      <c r="G127">
+        <f t="shared" si="50"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="H127" s="13">
+        <f t="shared" ref="H127:H133" si="60">ABS(F127-E127)</f>
+        <v>24.700000000000003</v>
+      </c>
+      <c r="L127" s="12"/>
+      <c r="M127">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N127">
+        <v>9.4</v>
+      </c>
+      <c r="O127">
+        <v>94</v>
+      </c>
+      <c r="P127">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="Q127">
+        <f t="shared" si="52"/>
+        <v>0.59999999999999964</v>
+      </c>
+      <c r="R127" s="13">
+        <f t="shared" ref="R127:R133" si="61">ABS(P127-O127)</f>
+        <v>17.599999999999994</v>
+      </c>
+      <c r="V127" s="12"/>
+      <c r="W127">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="X127">
+        <v>7.3</v>
+      </c>
+      <c r="Y127">
+        <v>94</v>
+      </c>
+      <c r="Z127">
+        <v>83.5</v>
+      </c>
+      <c r="AA127">
+        <f t="shared" si="54"/>
+        <v>1.5000000000000009</v>
+      </c>
+      <c r="AB127" s="13">
+        <f t="shared" ref="AB127:AB133" si="62">ABS(Z127-Y127)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AG127" s="12"/>
+      <c r="AH127">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AJ127">
+        <v>94</v>
+      </c>
+      <c r="AK127">
+        <v>74.5</v>
+      </c>
+      <c r="AL127">
+        <f t="shared" si="56"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AM127" s="13">
+        <f t="shared" ref="AM127:AM133" si="63">ABS(AK127-AJ127)</f>
+        <v>19.5</v>
+      </c>
+      <c r="AR127" s="12"/>
+      <c r="AS127">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AT127">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AU127">
+        <v>94</v>
+      </c>
+      <c r="AV127">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="AW127">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AX127" s="13">
+        <f t="shared" ref="AX127:AX133" si="64">ABS(AV127-AU127)</f>
+        <v>15.099999999999994</v>
+      </c>
+    </row>
+    <row r="128" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B128" s="12"/>
+      <c r="C128">
+        <v>10</v>
+      </c>
+      <c r="D128">
+        <v>9.5</v>
+      </c>
+      <c r="E128">
+        <v>76</v>
+      </c>
+      <c r="F128">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="G128">
+        <f t="shared" si="50"/>
+        <v>0.5</v>
+      </c>
+      <c r="H128" s="13">
+        <f t="shared" si="60"/>
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="L128" s="12"/>
+      <c r="M128">
+        <v>10</v>
+      </c>
+      <c r="N128">
+        <v>9.6</v>
+      </c>
+      <c r="O128">
+        <v>76</v>
+      </c>
+      <c r="P128">
+        <v>85.6</v>
+      </c>
+      <c r="Q128">
+        <f t="shared" si="52"/>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="R128" s="13">
+        <f t="shared" si="61"/>
+        <v>9.5999999999999943</v>
+      </c>
+      <c r="V128" s="12"/>
+      <c r="W128">
+        <v>10</v>
+      </c>
+      <c r="X128">
+        <v>9</v>
+      </c>
+      <c r="Y128">
+        <v>76</v>
+      </c>
+      <c r="Z128">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="AA128">
+        <f t="shared" si="54"/>
+        <v>1</v>
+      </c>
+      <c r="AB128" s="13">
+        <f t="shared" si="62"/>
+        <v>1.5999999999999943</v>
+      </c>
+      <c r="AG128" s="12"/>
+      <c r="AH128">
+        <v>10</v>
+      </c>
+      <c r="AJ128">
+        <v>76</v>
+      </c>
+      <c r="AK128">
+        <v>172</v>
+      </c>
+      <c r="AL128">
+        <f t="shared" si="56"/>
+        <v>10</v>
+      </c>
+      <c r="AM128" s="13">
+        <f t="shared" si="63"/>
+        <v>96</v>
+      </c>
+      <c r="AR128" s="12"/>
+      <c r="AS128">
+        <v>10</v>
+      </c>
+      <c r="AT128">
+        <v>10.15</v>
+      </c>
+      <c r="AU128">
+        <v>76</v>
+      </c>
+      <c r="AV128">
+        <v>89.7</v>
+      </c>
+      <c r="AW128">
+        <f t="shared" si="58"/>
+        <v>0.15000000000000036</v>
+      </c>
+      <c r="AX128" s="13">
+        <f t="shared" si="64"/>
+        <v>13.700000000000003</v>
+      </c>
+    </row>
+    <row r="129" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B129" s="6"/>
+      <c r="C129" s="7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D129" s="7">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E129" s="7">
+        <v>94</v>
+      </c>
+      <c r="F129" s="7">
+        <v>83.2</v>
+      </c>
+      <c r="G129" s="7">
+        <f t="shared" si="50"/>
+        <v>0.89999999999999858</v>
+      </c>
+      <c r="H129" s="13">
+        <f t="shared" si="60"/>
+        <v>10.799999999999997</v>
+      </c>
+      <c r="L129" s="6"/>
+      <c r="M129" s="7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N129" s="7">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="O129" s="7">
+        <v>94</v>
+      </c>
+      <c r="P129" s="7">
+        <v>113</v>
+      </c>
+      <c r="Q129" s="7">
+        <f t="shared" si="52"/>
+        <v>1</v>
+      </c>
+      <c r="R129" s="13">
+        <f t="shared" si="61"/>
+        <v>19</v>
+      </c>
+      <c r="V129" s="6"/>
+      <c r="W129" s="7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="X129" s="7">
+        <v>9</v>
+      </c>
+      <c r="Y129" s="7">
+        <v>94</v>
+      </c>
+      <c r="Z129" s="7">
+        <v>87</v>
+      </c>
+      <c r="AA129" s="7">
+        <f t="shared" si="54"/>
+        <v>0.19999999999999929</v>
+      </c>
+      <c r="AB129" s="13">
+        <f t="shared" si="62"/>
+        <v>7</v>
+      </c>
+      <c r="AG129" s="6"/>
+      <c r="AH129" s="7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AI129" s="7"/>
+      <c r="AJ129" s="7">
+        <v>94</v>
+      </c>
+      <c r="AK129" s="7">
+        <v>165</v>
+      </c>
+      <c r="AL129" s="7">
+        <f t="shared" si="56"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AM129" s="13">
+        <f t="shared" si="63"/>
+        <v>71</v>
+      </c>
+      <c r="AR129" s="6"/>
+      <c r="AS129" s="7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AT129" s="7">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AU129" s="7">
+        <v>94</v>
+      </c>
+      <c r="AV129" s="7">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="AW129" s="7">
+        <f t="shared" si="58"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="AX129" s="13">
+        <f t="shared" si="64"/>
+        <v>25.099999999999994</v>
+      </c>
+    </row>
+    <row r="130" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B130" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C130" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="D130" s="4">
+        <v>10.7</v>
+      </c>
+      <c r="E130" s="4">
+        <v>95</v>
+      </c>
+      <c r="F130" s="4">
+        <v>68.7</v>
+      </c>
+      <c r="G130" s="4">
+        <f t="shared" si="50"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="H130" s="5">
+        <f t="shared" si="60"/>
+        <v>26.299999999999997</v>
+      </c>
+      <c r="L130" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M130" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="N130" s="4">
+        <v>10.1</v>
+      </c>
+      <c r="O130" s="4">
+        <v>95</v>
+      </c>
+      <c r="P130" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="Q130" s="4">
+        <f t="shared" si="52"/>
+        <v>0.70000000000000107</v>
+      </c>
+      <c r="R130" s="5">
+        <f t="shared" si="61"/>
+        <v>1.4000000000000057</v>
+      </c>
+      <c r="V130" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W130" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="X130" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="Y130" s="4">
+        <v>95</v>
+      </c>
+      <c r="Z130" s="4">
+        <v>88.5</v>
+      </c>
+      <c r="AA130" s="4">
+        <f t="shared" si="54"/>
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="AB130" s="5">
+        <f t="shared" si="62"/>
+        <v>6.5</v>
+      </c>
+      <c r="AG130" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH130" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="AI130" s="4"/>
+      <c r="AJ130" s="4">
+        <v>95</v>
+      </c>
+      <c r="AK130" s="4">
+        <v>106.5</v>
+      </c>
+      <c r="AL130" s="4">
+        <f t="shared" si="56"/>
+        <v>10.8</v>
+      </c>
+      <c r="AM130" s="5">
+        <f t="shared" si="63"/>
+        <v>11.5</v>
+      </c>
+      <c r="AR130" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS130" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="AT130" s="4">
+        <v>10.6</v>
+      </c>
+      <c r="AU130" s="4">
+        <v>95</v>
+      </c>
+      <c r="AV130" s="4">
+        <v>86.7</v>
+      </c>
+      <c r="AW130" s="4">
+        <f t="shared" si="58"/>
+        <v>0.20000000000000107</v>
+      </c>
+      <c r="AX130" s="5">
+        <f t="shared" si="64"/>
+        <v>8.2999999999999972</v>
+      </c>
+    </row>
+    <row r="131" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B131" s="12"/>
+      <c r="C131">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D131">
+        <v>8.9</v>
+      </c>
+      <c r="E131">
+        <v>101</v>
+      </c>
+      <c r="F131">
+        <v>72.599999999999994</v>
+      </c>
+      <c r="G131">
+        <f t="shared" si="50"/>
+        <v>0.29999999999999893</v>
+      </c>
+      <c r="H131" s="13">
+        <f t="shared" si="60"/>
+        <v>28.400000000000006</v>
+      </c>
+      <c r="L131" s="12"/>
+      <c r="M131">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N131">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="O131">
+        <v>101</v>
+      </c>
+      <c r="P131">
+        <v>50.5</v>
+      </c>
+      <c r="Q131">
+        <f t="shared" si="52"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="R131" s="13">
+        <f t="shared" si="61"/>
+        <v>50.5</v>
+      </c>
+      <c r="V131" s="12"/>
+      <c r="W131">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="X131">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Y131">
+        <v>101</v>
+      </c>
+      <c r="Z131">
+        <v>95.8</v>
+      </c>
+      <c r="AA131">
+        <f t="shared" si="54"/>
+        <v>1</v>
+      </c>
+      <c r="AB131" s="13">
+        <f t="shared" si="62"/>
+        <v>5.2000000000000028</v>
+      </c>
+      <c r="AG131" s="12"/>
+      <c r="AH131">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AJ131">
+        <v>101</v>
+      </c>
+      <c r="AK131">
+        <v>64.3</v>
+      </c>
+      <c r="AL131">
+        <f t="shared" si="56"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AM131" s="13">
+        <f t="shared" si="63"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="AR131" s="12"/>
+      <c r="AS131">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AT131">
+        <v>8.6</v>
+      </c>
+      <c r="AU131">
+        <v>101</v>
+      </c>
+      <c r="AV131">
+        <v>64.3</v>
+      </c>
+      <c r="AW131">
+        <f t="shared" si="58"/>
+        <v>0.59999999999999964</v>
+      </c>
+      <c r="AX131" s="13">
+        <f t="shared" si="64"/>
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+    <row r="132" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B132" s="12"/>
+      <c r="C132">
+        <v>10</v>
+      </c>
+      <c r="D132">
+        <v>7.1</v>
+      </c>
+      <c r="E132">
+        <v>90</v>
+      </c>
+      <c r="F132">
+        <v>70.8</v>
+      </c>
+      <c r="G132">
+        <f t="shared" si="50"/>
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="H132" s="13">
+        <f t="shared" si="60"/>
+        <v>19.200000000000003</v>
+      </c>
+      <c r="L132" s="12"/>
+      <c r="M132">
+        <v>10</v>
+      </c>
+      <c r="N132">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="O132">
+        <v>90</v>
+      </c>
+      <c r="P132">
+        <v>58.8</v>
+      </c>
+      <c r="Q132">
+        <f t="shared" si="52"/>
+        <v>1.1999999999999993</v>
+      </c>
+      <c r="R132" s="13">
+        <f t="shared" si="61"/>
+        <v>31.200000000000003</v>
+      </c>
+      <c r="V132" s="12"/>
+      <c r="W132">
+        <v>10</v>
+      </c>
+      <c r="X132">
+        <v>7</v>
+      </c>
+      <c r="Y132">
+        <v>90</v>
+      </c>
+      <c r="Z132">
+        <v>88.5</v>
+      </c>
+      <c r="AA132">
+        <f t="shared" si="54"/>
+        <v>3</v>
+      </c>
+      <c r="AB132" s="13">
+        <f t="shared" si="62"/>
+        <v>1.5</v>
+      </c>
+      <c r="AG132" s="12"/>
+      <c r="AH132">
+        <v>10</v>
+      </c>
+      <c r="AJ132">
+        <v>90</v>
+      </c>
+      <c r="AK132">
+        <v>102</v>
+      </c>
+      <c r="AL132">
+        <f t="shared" si="56"/>
+        <v>10</v>
+      </c>
+      <c r="AM132" s="13">
+        <f t="shared" si="63"/>
+        <v>12</v>
+      </c>
+      <c r="AR132" s="12"/>
+      <c r="AS132">
+        <v>10</v>
+      </c>
+      <c r="AT132">
+        <v>6.6</v>
+      </c>
+      <c r="AU132">
+        <v>90</v>
+      </c>
+      <c r="AV132">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="AW132">
+        <f t="shared" si="58"/>
         <v>3.4000000000000004</v>
       </c>
-      <c r="AX123" s="13">
+      <c r="AX132" s="13">
         <f t="shared" si="64"/>
         <v>14.400000000000006</v>
       </c>
     </row>
-    <row r="124" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="B124" s="6"/>
-      <c r="C124" s="7">
+    <row r="133" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="B133" s="6"/>
+      <c r="C133" s="7">
         <v>10.8</v>
       </c>
-      <c r="D124" s="7">
+      <c r="D133" s="7">
         <v>8</v>
       </c>
-      <c r="E124" s="7">
+      <c r="E133" s="7">
         <v>75</v>
       </c>
-      <c r="F124" s="7">
+      <c r="F133" s="7">
         <v>65</v>
       </c>
-      <c r="G124" s="7">
+      <c r="G133" s="7">
         <f t="shared" si="50"/>
         <v>2.8000000000000007</v>
       </c>
-      <c r="H124" s="8">
+      <c r="H133" s="8">
         <f t="shared" si="60"/>
         <v>10</v>
       </c>
-      <c r="L124" s="6"/>
-      <c r="M124" s="7">
+      <c r="L133" s="6"/>
+      <c r="M133" s="7">
         <v>10.8</v>
       </c>
-      <c r="N124" s="7">
+      <c r="N133" s="7">
         <v>9.4</v>
       </c>
-      <c r="O124" s="7">
+      <c r="O133" s="7">
         <v>75</v>
       </c>
-      <c r="P124" s="7">
+      <c r="P133" s="7">
         <v>53.2</v>
       </c>
-      <c r="Q124" s="7">
+      <c r="Q133" s="7">
         <f t="shared" si="52"/>
         <v>1.4000000000000004</v>
       </c>
-      <c r="R124" s="13">
+      <c r="R133" s="13">
         <f t="shared" si="61"/>
         <v>21.799999999999997</v>
       </c>
-      <c r="V124" s="6"/>
-      <c r="W124" s="7">
+      <c r="V133" s="6"/>
+      <c r="W133" s="7">
         <v>10.8</v>
       </c>
-      <c r="X124" s="7">
+      <c r="X133" s="7">
         <v>7.3</v>
       </c>
-      <c r="Y124" s="7">
+      <c r="Y133" s="7">
         <v>75</v>
       </c>
-      <c r="Z124" s="7">
+      <c r="Z133" s="7">
         <v>86.1</v>
       </c>
-      <c r="AA124" s="7">
+      <c r="AA133" s="7">
         <f t="shared" si="54"/>
         <v>3.5000000000000009</v>
       </c>
-      <c r="AB124" s="13">
+      <c r="AB133" s="13">
         <f t="shared" si="62"/>
         <v>11.099999999999994</v>
       </c>
-      <c r="AG124" s="6"/>
-      <c r="AH124" s="7">
+      <c r="AG133" s="6"/>
+      <c r="AH133" s="7">
         <v>10.8</v>
       </c>
-      <c r="AI124" s="7"/>
-      <c r="AJ124" s="7">
+      <c r="AI133" s="7"/>
+      <c r="AJ133" s="7">
         <v>75</v>
       </c>
-      <c r="AK124" s="7">
+      <c r="AK133" s="7">
         <v>181.5</v>
       </c>
-      <c r="AL124" s="7">
+      <c r="AL133" s="7">
         <f t="shared" si="56"/>
         <v>10.8</v>
       </c>
-      <c r="AM124" s="8">
+      <c r="AM133" s="8">
         <f t="shared" si="63"/>
         <v>106.5</v>
       </c>
-      <c r="AR124" s="6"/>
-      <c r="AS124" s="7">
+      <c r="AR133" s="6"/>
+      <c r="AS133" s="7">
         <v>10.8</v>
       </c>
-      <c r="AT124" s="7">
+      <c r="AT133" s="7">
         <v>9.4</v>
       </c>
-      <c r="AU124" s="7">
+      <c r="AU133" s="7">
         <v>75</v>
       </c>
-      <c r="AV124" s="7">
+      <c r="AV133" s="7">
         <v>89.8</v>
       </c>
-      <c r="AW124" s="7">
+      <c r="AW133" s="7">
         <f t="shared" si="58"/>
         <v>1.4000000000000004</v>
       </c>
-      <c r="AX124" s="13">
+      <c r="AX133" s="13">
         <f t="shared" si="64"/>
         <v>14.799999999999997</v>
       </c>
     </row>
-    <row r="125" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="G125">
-        <f>AVERAGE(G2:G124)</f>
-        <v>0.62926829268292683</v>
-      </c>
-      <c r="H125">
-        <f>AVERAGE(H2:H124)</f>
-        <v>20.295121951219503</v>
-      </c>
-      <c r="Q125">
-        <f>AVERAGE(Q2:Q124)</f>
-        <v>0.64146341463414647</v>
-      </c>
-      <c r="R125" s="4">
-        <f>AVERAGE(R2:R124)</f>
-        <v>22.600813008130082</v>
-      </c>
-      <c r="AA125">
-        <f>AVERAGE(AA2:AA124)</f>
-        <v>0.91707317073170702</v>
-      </c>
-      <c r="AB125" s="4">
-        <f>AVERAGE(AB2:AB124)</f>
-        <v>10.59186991869918</v>
-      </c>
-      <c r="AM125">
-        <f>AVERAGE(AM2:AM124)</f>
-        <v>42.395121951219515</v>
-      </c>
-      <c r="AW125">
-        <f>AVERAGE(AW2:AW124)</f>
-        <v>0.6084552845528457</v>
-      </c>
-      <c r="AX125" s="4">
-        <f>AVERAGE(AX2:AX124)</f>
-        <v>20.345528455284551</v>
+    <row r="134" spans="2:50" x14ac:dyDescent="0.25">
+      <c r="G134">
+        <f>AVERAGE(G2:G133)</f>
+        <v>0.60151515151515156</v>
+      </c>
+      <c r="H134">
+        <f>AVERAGE(H2:H133)</f>
+        <v>19.684090909090902</v>
+      </c>
+      <c r="Q134">
+        <f>AVERAGE(Q2:Q133)</f>
+        <v>0.63181818181818195</v>
+      </c>
+      <c r="R134" s="4">
+        <f>AVERAGE(R2:R133)</f>
+        <v>22.259848484848487</v>
+      </c>
+      <c r="AA134">
+        <f>AVERAGE(AA2:AA133)</f>
+        <v>0.90984848484848468</v>
+      </c>
+      <c r="AB134" s="4">
+        <f>AVERAGE(AB2:AB133)</f>
+        <v>10.979545454545447</v>
+      </c>
+      <c r="AM134">
+        <f>AVERAGE(AM2:AM133)</f>
+        <v>40.844318181818188</v>
+      </c>
+      <c r="AW134">
+        <f>AVERAGE(AW2:AW133)</f>
+        <v>0.61772727272727301</v>
+      </c>
+      <c r="AX134" s="4">
+        <f>AVERAGE(AX2:AX133)</f>
+        <v>20.440151515151513</v>
       </c>
     </row>
   </sheetData>
